--- a/Project/PlanningCenterScheduleUploader/PlanningCenterAPI.Test/Schedule.xlsx
+++ b/Project/PlanningCenterScheduleUploader/PlanningCenterAPI.Test/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\GitHub\PlanningCenterScheduleUploader\Project\PlanningCenterScheduleUploader\PlanningCenterAPI.Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B174B915-4E7B-498C-8370-2FBE82AAA346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7374EE1-0DA1-4EBC-BC96-867D96C254CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{270EC0F9-CA9F-4B8F-8137-AAC43B2367E2}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
   <si>
     <t>Service Type</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Date</t>
   </si>
   <si>
-    <t>Conner Milne</t>
-  </si>
-  <si>
     <t>Ransome Madziwa</t>
   </si>
   <si>
@@ -74,6 +71,9 @@
   </si>
   <si>
     <t>Devlyn van der Walt</t>
+  </si>
+  <si>
+    <t>Connor Milne</t>
   </si>
 </sst>
 </file>
@@ -81,7 +81,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="[$-1C09]dd\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-1C09]dd\ mmmm\ yyyy;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -123,8 +123,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCAD8E2-0228-42F9-9D20-C4D47ACFB5CC}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -463,58 +463,72 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>46117</v>
+        <v>46115</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>46124</v>
+        <v>46117</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>46131</v>
+        <v>46124</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
+        <v>46131</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>46138</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -550,5 +564,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Project/PlanningCenterScheduleUploader/PlanningCenterAPI.Test/Schedule.xlsx
+++ b/Project/PlanningCenterScheduleUploader/PlanningCenterAPI.Test/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\GitHub\PlanningCenterScheduleUploader\Project\PlanningCenterScheduleUploader\PlanningCenterAPI.Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7374EE1-0DA1-4EBC-BC96-867D96C254CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3652E56A-1880-4102-9561-E87448340688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{270EC0F9-CA9F-4B8F-8137-AAC43B2367E2}"/>
   </bookViews>
@@ -40,40 +40,40 @@
     <t>Service Type</t>
   </si>
   <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Camera</t>
+  </si>
+  <si>
+    <t>Editor</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Ransome Madziwa</t>
+  </si>
+  <si>
+    <t>Ramon Ferreira</t>
+  </si>
+  <si>
+    <t>Wale Adeniran</t>
+  </si>
+  <si>
+    <t>Devlyn van der Walt</t>
+  </si>
+  <si>
+    <t>Connor Milne</t>
+  </si>
+  <si>
     <t>Sunday and Other Services</t>
   </si>
   <si>
-    <t>Team</t>
-  </si>
-  <si>
     <t>Live Stream</t>
   </si>
   <si>
-    <t>Camera</t>
-  </si>
-  <si>
     <t>Comms</t>
-  </si>
-  <si>
-    <t>Editor</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Ransome Madziwa</t>
-  </si>
-  <si>
-    <t>Ramon Ferreira</t>
-  </si>
-  <si>
-    <t>Wale Adeniran</t>
-  </si>
-  <si>
-    <t>Devlyn van der Walt</t>
-  </si>
-  <si>
-    <t>Connor Milne</t>
   </si>
 </sst>
 </file>
@@ -449,16 +449,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -466,13 +466,13 @@
         <v>46115</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -480,13 +480,13 @@
         <v>46117</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -494,13 +494,13 @@
         <v>46124</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -508,13 +508,13 @@
         <v>46131</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -522,13 +522,13 @@
         <v>46138</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -551,15 +551,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Project/PlanningCenterScheduleUploader/PlanningCenterAPI.Test/Schedule.xlsx
+++ b/Project/PlanningCenterScheduleUploader/PlanningCenterAPI.Test/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\GitHub\PlanningCenterScheduleUploader\Project\PlanningCenterScheduleUploader\PlanningCenterAPI.Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3652E56A-1880-4102-9561-E87448340688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52A05EF-F2A4-4C41-BF00-83DAC23F62DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{270EC0F9-CA9F-4B8F-8137-AAC43B2367E2}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="15">
   <si>
     <t>Service Type</t>
   </si>
@@ -43,9 +43,6 @@
     <t>Team</t>
   </si>
   <si>
-    <t>Camera</t>
-  </si>
-  <si>
     <t>Editor</t>
   </si>
   <si>
@@ -55,9 +52,6 @@
     <t>Ransome Madziwa</t>
   </si>
   <si>
-    <t>Ramon Ferreira</t>
-  </si>
-  <si>
     <t>Wale Adeniran</t>
   </si>
   <si>
@@ -74,6 +68,18 @@
   </si>
   <si>
     <t>Comms</t>
+  </si>
+  <si>
+    <t>Camera First Service</t>
+  </si>
+  <si>
+    <t>Camera Second Service</t>
+  </si>
+  <si>
+    <t>Byron Raaff</t>
+  </si>
+  <si>
+    <t>Tando Khoza</t>
   </si>
 </sst>
 </file>
@@ -439,96 +445,115 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCAD8E2-0228-42F9-9D20-C4D47ACFB5CC}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>46115</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>46117</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>46124</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>46131</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>46138</v>
       </c>
       <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
+      <c r="E6" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -551,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -559,7 +584,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Project/PlanningCenterScheduleUploader/PlanningCenterAPI.Test/Schedule.xlsx
+++ b/Project/PlanningCenterScheduleUploader/PlanningCenterAPI.Test/Schedule.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <x:workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\GitHub\PlanningCenterScheduleUploader\Project\PlanningCenterScheduleUploader\PlanningCenterAPI.Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52A05EF-F2A4-4C41-BF00-83DAC23F62DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{270EC0F9-CA9F-4B8F-8137-AAC43B2367E2}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Schedule" sheetId="2" r:id="rId1"/>
-    <sheet name="Setup" sheetId="1" r:id="rId2"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <x:bookViews>
+    <x:workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="0" activeTab="0" xr2:uid="{270EC0F9-CA9F-4B8F-8137-AAC43B2367E2}"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="Schedule" sheetId="2" r:id="rId1"/>
+    <x:sheet name="Setup" sheetId="1" r:id="rId2"/>
+  </x:sheets>
+  <x:definedNames/>
+  <x:calcPr calcId="191029"/>
+  <x:extLst>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+    </x:ext>
+    <x:ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
@@ -29,123 +30,150 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+    </x:ext>
+  </x:extLst>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="15">
-  <si>
-    <t>Service Type</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Editor</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Ransome Madziwa</t>
-  </si>
-  <si>
-    <t>Wale Adeniran</t>
-  </si>
-  <si>
-    <t>Devlyn van der Walt</t>
-  </si>
-  <si>
-    <t>Connor Milne</t>
-  </si>
-  <si>
-    <t>Sunday and Other Services</t>
-  </si>
-  <si>
-    <t>Live Stream</t>
-  </si>
-  <si>
-    <t>Comms</t>
-  </si>
-  <si>
-    <t>Camera First Service</t>
-  </si>
-  <si>
-    <t>Camera Second Service</t>
-  </si>
-  <si>
-    <t>Byron Raaff</t>
-  </si>
-  <si>
-    <t>Tando Khoza</t>
-  </si>
-</sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:si>
+    <x:t>Date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Camera First Service</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Camera Second Service</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comms</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Editor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Byron Raaff</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tando Khoza</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wale Adeniran</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connor Milne</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ransome Madziwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Devlyn van der Walt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Service Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sunday and Other Services</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Team</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Live Stream</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-1C09]dd\ mmmm\ yyyy;@"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2 xr">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="164" formatCode="[$-1C09]dd\ mmmm\ yyyy;@"/>
+  </x:numFmts>
+  <x:fonts count="3" x14ac:knownFonts="1">
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="3">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF00"/>
+      </x:patternFill>
+    </x:fill>
+  </x:fills>
+  <x:borders count="1">
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="5">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+  </x:cellStyleXfs>
+  <x:cellXfs count="5">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </x:cellStyles>
+  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <x:extLst>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+    </x:ext>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
+    </x:ext>
+  </x:extLst>
+</x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -444,151 +472,163 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCAD8E2-0228-42F9-9D20-C4D47ACFB5CC}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="19" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>46115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <v>46117</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>46124</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>46131</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>46138</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{FDCAD8E2-0228-42F9-9D20-C4D47ACFB5CC}" mc:Ignorable="x14ac xr xr2 xr3">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:E6"/>
+  <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.425781" style="3" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="19.140625" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="21.855469" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="5" width="19" style="0" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A1" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A2" s="3">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A3" s="3">
+        <x:v>46117</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A4" s="3">
+        <x:v>46124</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A5" s="3">
+        <x:v>46131</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A6" s="3">
+        <x:v>46138</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:pageSetup paperSize="9" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" r:id="rId1"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995546DB-B735-4DE5-BB12-7B0E62843443}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{995546DB-B735-4DE5-BB12-7B0E62843443}" mc:Ignorable="x14ac xr xr2 xr3">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:B2"/>
+  <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12.855469" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24.855469" style="0" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <x:c r="A1" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <x:c r="A2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:pageSetup paperSize="9" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" r:id="rId1"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/Project/PlanningCenterScheduleUploader/PlanningCenterAPI.Test/Schedule.xlsx
+++ b/Project/PlanningCenterScheduleUploader/PlanningCenterAPI.Test/Schedule.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zionn\Documents\GitHub\PlanningCenterScheduleUploader\Project\PlanningCenterScheduleUploader\PlanningCenterAPI.Test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51677FA-3363-499C-89E1-3F369B31515C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="1380" yWindow="1380" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Schedule" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Setup" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Schedule" sheetId="1" r:id="rId1"/>
+    <sheet name="Setup" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -23,60 +28,59 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="15">
   <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camera First Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camera Second Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Editor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Byron Raaff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tando Khoza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wale Adeniran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Milne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ransome Madziwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devlyn van der Walt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunday and Other Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live Stream</t>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Camera First Service</t>
+  </si>
+  <si>
+    <t>Camera Second Service</t>
+  </si>
+  <si>
+    <t>Comms</t>
+  </si>
+  <si>
+    <t>Editor</t>
+  </si>
+  <si>
+    <t>Byron Raaff</t>
+  </si>
+  <si>
+    <t>Tando Khoza</t>
+  </si>
+  <si>
+    <t>Wale Adeniran</t>
+  </si>
+  <si>
+    <t>Connor Milne</t>
+  </si>
+  <si>
+    <t>Ransome Madziwa</t>
+  </si>
+  <si>
+    <t>Devlyn van der Walt</t>
+  </si>
+  <si>
+    <t>Service Type</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Live Stream</t>
+  </si>
+  <si>
+    <t>Sunday Service</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="[$-1C09]dd\ mmmm\ yyyy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-1C09]dd\ mmmm\ yyyy;@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,22 +89,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -117,7 +106,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -125,62 +114,33 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -222,12 +182,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -259,7 +219,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -283,7 +243,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -343,29 +303,28 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="19"/>
+    <col min="1" max="1" width="15" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" customWidth="1"/>
+    <col min="4" max="5" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -382,137 +341,124 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>46208</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>46215</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>46222</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>46229</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>46236</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24.86"/>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>14</v>
-      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Project/PlanningCenterScheduleUploader/PlanningCenterAPI.Test/Schedule.xlsx
+++ b/Project/PlanningCenterScheduleUploader/PlanningCenterAPI.Test/Schedule.xlsx
@@ -1,22 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zionn\Documents\GitHub\PlanningCenterScheduleUploader\Project\PlanningCenterScheduleUploader\PlanningCenterAPI.Test\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51677FA-3363-499C-89E1-3F369B31515C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="1380" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Schedule" sheetId="1" r:id="rId1"/>
-    <sheet name="Setup" sheetId="2" r:id="rId2"/>
+    <sheet name="Schedule" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Setup" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -26,61 +21,62 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="15">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Camera First Service</t>
-  </si>
-  <si>
-    <t>Camera Second Service</t>
-  </si>
-  <si>
-    <t>Comms</t>
-  </si>
-  <si>
-    <t>Editor</t>
-  </si>
-  <si>
-    <t>Byron Raaff</t>
-  </si>
-  <si>
-    <t>Tando Khoza</t>
-  </si>
-  <si>
-    <t>Wale Adeniran</t>
-  </si>
-  <si>
-    <t>Connor Milne</t>
-  </si>
-  <si>
-    <t>Ransome Madziwa</t>
-  </si>
-  <si>
-    <t>Devlyn van der Walt</t>
-  </si>
-  <si>
-    <t>Service Type</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Live Stream</t>
-  </si>
-  <si>
-    <t>Sunday Service</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camera First Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camera Second Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Editor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byron Raaff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tando Khoza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wale Adeniran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Milne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ransome Madziwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devlyn van der Walt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunday Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live Stream</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-1C09]dd\ mmmm\ yyyy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="[$-1C09]dd\ mmmm\ yyyy;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,7 +85,22 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -106,7 +117,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -114,33 +125,62 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -182,12 +222,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -219,7 +259,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -243,7 +283,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -303,28 +343,29 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="15" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="3" max="3" width="21.85546875" customWidth="1"/>
-    <col min="4" max="5" width="19" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -341,124 +382,120 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>46208</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="0" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>46215</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="0" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>46222</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="0" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>46229</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B5" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="0" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>46236</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24.86"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>